--- a/Projeto_1/data/Episodios_Simpsons.xlsx
+++ b/Projeto_1/data/Episodios_Simpsons.xlsx
@@ -2268,17 +2268,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/Projeto_1/data/Episodios_Simpsons.xlsx
+++ b/Projeto_1/data/Episodios_Simpsons.xlsx
@@ -2268,17 +2268,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TBA</t>
         </is>
       </c>
     </row>
